--- a/output/pdf_financials_xlsx/HWG.xlsx
+++ b/output/pdf_financials_xlsx/HWG.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.005517</v>
+        <v>1.611312</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.001829</v>
+        <v>1.829711</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.199033</v>
+        <v>3.220911</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.005517</v>
+        <v>-1.611312</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.001829</v>
+        <v>-1.829711</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.199033</v>
+        <v>-3.220911</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.087612</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.050022</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.046201</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.21068</v>
+        <v>0.123068</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.179419</v>
+        <v>-4.229441</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.988153</v>
+        <v>-2.034354</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.447398</v>
+        <v>0.359786</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.959039</v>
+        <v>-4.009061</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.778117</v>
+        <v>-1.824318</v>
       </c>
     </row>
     <row r="30">
@@ -2419,13 +2419,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.213215</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.210426</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.211805</v>
       </c>
     </row>
     <row r="125">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.213215</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.210426</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.211805</v>
       </c>
     </row>
     <row r="126">
@@ -4352,7 +4352,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>-0.213215</v>
       </c>
@@ -6143,17 +6147,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>-1.611312</v>
+        <v>1.611312</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>-1.829711</v>
+        <v>1.829711</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>-3.220911</v>
+        <v>3.220911</v>
       </c>
     </row>
     <row r="115">
@@ -6230,7 +6234,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
